--- a/examples/ltd-latest/Salesinvoice.xlsx
+++ b/examples/ltd-latest/Salesinvoice.xlsx
@@ -7750,930 +7750,1209 @@
         <v>20</v>
       </c>
       <c r="G6" s="81" t="str">
+        <f aca="false">IF(F6&gt;0,C6-F6," ")</f>
+        <v> </v>
+      </c>
+      <c r="H6" s="82" t="str">
         <f aca="false">IF(F6&gt;0,(C6-F6)*100/C6," ")</f>
         <v> </v>
       </c>
-      <c r="H6" s="82"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G7" s="81" t="str">
+        <f aca="false">IF(F7&gt;0,C7-F7," ")</f>
+        <v> </v>
+      </c>
+      <c r="H7" s="82" t="str">
         <f aca="false">IF(F7&gt;0,(C7-F7)*100/C7," ")</f>
         <v> </v>
       </c>
-      <c r="H7" s="82"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G8" s="81" t="str">
+        <f aca="false">IF(F8&gt;0,C8-F8," ")</f>
+        <v> </v>
+      </c>
+      <c r="H8" s="82" t="str">
         <f aca="false">IF(F8&gt;0,(C8-F8)*100/C8," ")</f>
         <v> </v>
       </c>
-      <c r="H8" s="82"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G9" s="81" t="str">
+        <f aca="false">IF(F9&gt;0,C9-F9," ")</f>
+        <v> </v>
+      </c>
+      <c r="H9" s="82" t="str">
         <f aca="false">IF(F9&gt;0,(C9-F9)*100/C9," ")</f>
         <v> </v>
       </c>
-      <c r="H9" s="82"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G10" s="81" t="str">
+        <f aca="false">IF(F10&gt;0,C10-F10," ")</f>
+        <v> </v>
+      </c>
+      <c r="H10" s="82" t="str">
         <f aca="false">IF(F10&gt;0,(C10-F10)*100/C10," ")</f>
         <v> </v>
       </c>
-      <c r="H10" s="82"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G11" s="81" t="str">
+        <f aca="false">IF(F11&gt;0,C11-F11," ")</f>
+        <v> </v>
+      </c>
+      <c r="H11" s="82" t="str">
         <f aca="false">IF(F11&gt;0,(C11-F11)*100/C11," ")</f>
         <v> </v>
       </c>
-      <c r="H11" s="82"/>
     </row>
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G12" s="81" t="str">
+        <f aca="false">IF(F12&gt;0,C12-F12," ")</f>
+        <v> </v>
+      </c>
+      <c r="H12" s="82" t="str">
         <f aca="false">IF(F12&gt;0,(C12-F12)*100/C12," ")</f>
         <v> </v>
       </c>
-      <c r="H12" s="82"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G13" s="81" t="str">
+        <f aca="false">IF(F13&gt;0,C13-F13," ")</f>
+        <v> </v>
+      </c>
+      <c r="H13" s="82" t="str">
         <f aca="false">IF(F13&gt;0,(C13-F13)*100/C13," ")</f>
         <v> </v>
       </c>
-      <c r="H13" s="82"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G14" s="81" t="str">
+        <f aca="false">IF(F14&gt;0,C14-F14," ")</f>
+        <v> </v>
+      </c>
+      <c r="H14" s="82" t="str">
         <f aca="false">IF(F14&gt;0,(C14-F14)*100/C14," ")</f>
         <v> </v>
       </c>
-      <c r="H14" s="82"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G15" s="81" t="str">
+        <f aca="false">IF(F15&gt;0,C15-F15," ")</f>
+        <v> </v>
+      </c>
+      <c r="H15" s="82" t="str">
         <f aca="false">IF(F15&gt;0,(C15-F15)*100/C15," ")</f>
         <v> </v>
       </c>
-      <c r="H15" s="82"/>
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G16" s="81" t="str">
+        <f aca="false">IF(F16&gt;0,C16-F16," ")</f>
+        <v> </v>
+      </c>
+      <c r="H16" s="82" t="str">
         <f aca="false">IF(F16&gt;0,(C16-F16)*100/C16," ")</f>
         <v> </v>
       </c>
-      <c r="H16" s="82"/>
     </row>
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G17" s="81" t="str">
+        <f aca="false">IF(F17&gt;0,C17-F17," ")</f>
+        <v> </v>
+      </c>
+      <c r="H17" s="82" t="str">
         <f aca="false">IF(F17&gt;0,(C17-F17)*100/C17," ")</f>
         <v> </v>
       </c>
-      <c r="H17" s="82"/>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G18" s="81" t="str">
+        <f aca="false">IF(F18&gt;0,C18-F18," ")</f>
+        <v> </v>
+      </c>
+      <c r="H18" s="82" t="str">
         <f aca="false">IF(F18&gt;0,(C18-F18)*100/C18," ")</f>
         <v> </v>
       </c>
-      <c r="H18" s="82"/>
     </row>
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G19" s="81" t="str">
+        <f aca="false">IF(F19&gt;0,C19-F19," ")</f>
+        <v> </v>
+      </c>
+      <c r="H19" s="82" t="str">
         <f aca="false">IF(F19&gt;0,(C19-F19)*100/C19," ")</f>
         <v> </v>
       </c>
-      <c r="H19" s="82"/>
     </row>
     <row r="20" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G20" s="81" t="str">
+        <f aca="false">IF(F20&gt;0,C20-F20," ")</f>
+        <v> </v>
+      </c>
+      <c r="H20" s="82" t="str">
         <f aca="false">IF(F20&gt;0,(C20-F20)*100/C20," ")</f>
         <v> </v>
       </c>
-      <c r="H20" s="82"/>
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G21" s="81" t="str">
+        <f aca="false">IF(F21&gt;0,C21-F21," ")</f>
+        <v> </v>
+      </c>
+      <c r="H21" s="82" t="str">
         <f aca="false">IF(F21&gt;0,(C21-F21)*100/C21," ")</f>
         <v> </v>
       </c>
-      <c r="H21" s="82"/>
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G22" s="81" t="str">
+        <f aca="false">IF(F22&gt;0,C22-F22," ")</f>
+        <v> </v>
+      </c>
+      <c r="H22" s="82" t="str">
         <f aca="false">IF(F22&gt;0,(C22-F22)*100/C22," ")</f>
         <v> </v>
       </c>
-      <c r="H22" s="82"/>
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G23" s="81" t="str">
+        <f aca="false">IF(F23&gt;0,C23-F23," ")</f>
+        <v> </v>
+      </c>
+      <c r="H23" s="82" t="str">
         <f aca="false">IF(F23&gt;0,(C23-F23)*100/C23," ")</f>
         <v> </v>
       </c>
-      <c r="H23" s="82"/>
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G24" s="81" t="str">
+        <f aca="false">IF(F24&gt;0,C24-F24," ")</f>
+        <v> </v>
+      </c>
+      <c r="H24" s="82" t="str">
         <f aca="false">IF(F24&gt;0,(C24-F24)*100/C24," ")</f>
         <v> </v>
       </c>
-      <c r="H24" s="82"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G25" s="81" t="str">
+        <f aca="false">IF(F25&gt;0,C25-F25," ")</f>
+        <v> </v>
+      </c>
+      <c r="H25" s="82" t="str">
         <f aca="false">IF(F25&gt;0,(C25-F25)*100/C25," ")</f>
         <v> </v>
       </c>
-      <c r="H25" s="82"/>
     </row>
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G26" s="81" t="str">
+        <f aca="false">IF(F26&gt;0,C26-F26," ")</f>
+        <v> </v>
+      </c>
+      <c r="H26" s="82" t="str">
         <f aca="false">IF(F26&gt;0,(C26-F26)*100/C26," ")</f>
         <v> </v>
       </c>
-      <c r="H26" s="82"/>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G27" s="81" t="str">
+        <f aca="false">IF(F27&gt;0,C27-F27," ")</f>
+        <v> </v>
+      </c>
+      <c r="H27" s="82" t="str">
         <f aca="false">IF(F27&gt;0,(C27-F27)*100/C27," ")</f>
         <v> </v>
       </c>
-      <c r="H27" s="82"/>
     </row>
     <row r="28" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G28" s="81" t="str">
+        <f aca="false">IF(F28&gt;0,C28-F28," ")</f>
+        <v> </v>
+      </c>
+      <c r="H28" s="82" t="str">
         <f aca="false">IF(F28&gt;0,(C28-F28)*100/C28," ")</f>
         <v> </v>
       </c>
-      <c r="H28" s="82"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G29" s="81" t="str">
+        <f aca="false">IF(F29&gt;0,C29-F29," ")</f>
+        <v> </v>
+      </c>
+      <c r="H29" s="82" t="str">
         <f aca="false">IF(F29&gt;0,(C29-F29)*100/C29," ")</f>
         <v> </v>
       </c>
-      <c r="H29" s="82"/>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D30" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G30" s="81" t="str">
+        <f aca="false">IF(F30&gt;0,C30-F30," ")</f>
+        <v> </v>
+      </c>
+      <c r="H30" s="82" t="str">
         <f aca="false">IF(F30&gt;0,(C30-F30)*100/C30," ")</f>
         <v> </v>
       </c>
-      <c r="H30" s="82"/>
     </row>
     <row r="31" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G31" s="81" t="str">
+        <f aca="false">IF(F31&gt;0,C31-F31," ")</f>
+        <v> </v>
+      </c>
+      <c r="H31" s="82" t="str">
         <f aca="false">IF(F31&gt;0,(C31-F31)*100/C31," ")</f>
         <v> </v>
       </c>
-      <c r="H31" s="82"/>
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G32" s="81" t="str">
+        <f aca="false">IF(F32&gt;0,C32-F32," ")</f>
+        <v> </v>
+      </c>
+      <c r="H32" s="82" t="str">
         <f aca="false">IF(F32&gt;0,(C32-F32)*100/C32," ")</f>
         <v> </v>
       </c>
-      <c r="H32" s="82"/>
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G33" s="81" t="str">
+        <f aca="false">IF(F33&gt;0,C33-F33," ")</f>
+        <v> </v>
+      </c>
+      <c r="H33" s="82" t="str">
         <f aca="false">IF(F33&gt;0,(C33-F33)*100/C33," ")</f>
         <v> </v>
       </c>
-      <c r="H33" s="82"/>
     </row>
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G34" s="81" t="str">
+        <f aca="false">IF(F34&gt;0,C34-F34," ")</f>
+        <v> </v>
+      </c>
+      <c r="H34" s="82" t="str">
         <f aca="false">IF(F34&gt;0,(C34-F34)*100/C34," ")</f>
         <v> </v>
       </c>
-      <c r="H34" s="82"/>
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G35" s="81" t="str">
+        <f aca="false">IF(F35&gt;0,C35-F35," ")</f>
+        <v> </v>
+      </c>
+      <c r="H35" s="82" t="str">
         <f aca="false">IF(F35&gt;0,(C35-F35)*100/C35," ")</f>
         <v> </v>
       </c>
-      <c r="H35" s="82"/>
     </row>
     <row r="36" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G36" s="81" t="str">
+        <f aca="false">IF(F36&gt;0,C36-F36," ")</f>
+        <v> </v>
+      </c>
+      <c r="H36" s="82" t="str">
         <f aca="false">IF(F36&gt;0,(C36-F36)*100/C36," ")</f>
         <v> </v>
       </c>
-      <c r="H36" s="82"/>
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D37" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G37" s="81" t="str">
+        <f aca="false">IF(F37&gt;0,C37-F37," ")</f>
+        <v> </v>
+      </c>
+      <c r="H37" s="82" t="str">
         <f aca="false">IF(F37&gt;0,(C37-F37)*100/C37," ")</f>
         <v> </v>
       </c>
-      <c r="H37" s="82"/>
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G38" s="81" t="str">
+        <f aca="false">IF(F38&gt;0,C38-F38," ")</f>
+        <v> </v>
+      </c>
+      <c r="H38" s="82" t="str">
         <f aca="false">IF(F38&gt;0,(C38-F38)*100/C38," ")</f>
         <v> </v>
       </c>
-      <c r="H38" s="82"/>
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D39" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G39" s="81" t="str">
+        <f aca="false">IF(F39&gt;0,C39-F39," ")</f>
+        <v> </v>
+      </c>
+      <c r="H39" s="82" t="str">
         <f aca="false">IF(F39&gt;0,(C39-F39)*100/C39," ")</f>
         <v> </v>
       </c>
-      <c r="H39" s="82"/>
     </row>
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D40" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G40" s="81" t="str">
+        <f aca="false">IF(F40&gt;0,C40-F40," ")</f>
+        <v> </v>
+      </c>
+      <c r="H40" s="82" t="str">
         <f aca="false">IF(F40&gt;0,(C40-F40)*100/C40," ")</f>
         <v> </v>
       </c>
-      <c r="H40" s="82"/>
     </row>
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D41" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G41" s="81" t="str">
+        <f aca="false">IF(F41&gt;0,C41-F41," ")</f>
+        <v> </v>
+      </c>
+      <c r="H41" s="82" t="str">
         <f aca="false">IF(F41&gt;0,(C41-F41)*100/C41," ")</f>
         <v> </v>
       </c>
-      <c r="H41" s="82"/>
     </row>
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D42" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G42" s="81" t="str">
+        <f aca="false">IF(F42&gt;0,C42-F42," ")</f>
+        <v> </v>
+      </c>
+      <c r="H42" s="82" t="str">
         <f aca="false">IF(F42&gt;0,(C42-F42)*100/C42," ")</f>
         <v> </v>
       </c>
-      <c r="H42" s="82"/>
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D43" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G43" s="81" t="str">
+        <f aca="false">IF(F43&gt;0,C43-F43," ")</f>
+        <v> </v>
+      </c>
+      <c r="H43" s="82" t="str">
         <f aca="false">IF(F43&gt;0,(C43-F43)*100/C43," ")</f>
         <v> </v>
       </c>
-      <c r="H43" s="82"/>
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D44" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G44" s="81" t="str">
+        <f aca="false">IF(F44&gt;0,C44-F44," ")</f>
+        <v> </v>
+      </c>
+      <c r="H44" s="82" t="str">
         <f aca="false">IF(F44&gt;0,(C44-F44)*100/C44," ")</f>
         <v> </v>
       </c>
-      <c r="H44" s="82"/>
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D45" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G45" s="81" t="str">
+        <f aca="false">IF(F45&gt;0,C45-F45," ")</f>
+        <v> </v>
+      </c>
+      <c r="H45" s="82" t="str">
         <f aca="false">IF(F45&gt;0,(C45-F45)*100/C45," ")</f>
         <v> </v>
       </c>
-      <c r="H45" s="82"/>
     </row>
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G46" s="81" t="str">
+        <f aca="false">IF(F46&gt;0,C46-F46," ")</f>
+        <v> </v>
+      </c>
+      <c r="H46" s="82" t="str">
         <f aca="false">IF(F46&gt;0,(C46-F46)*100/C46," ")</f>
         <v> </v>
       </c>
-      <c r="H46" s="82"/>
     </row>
     <row r="47" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G47" s="81" t="str">
+        <f aca="false">IF(F47&gt;0,C47-F47," ")</f>
+        <v> </v>
+      </c>
+      <c r="H47" s="82" t="str">
         <f aca="false">IF(F47&gt;0,(C47-F47)*100/C47," ")</f>
         <v> </v>
       </c>
-      <c r="H47" s="82"/>
     </row>
     <row r="48" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D48" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G48" s="81" t="str">
+        <f aca="false">IF(F48&gt;0,C48-F48," ")</f>
+        <v> </v>
+      </c>
+      <c r="H48" s="82" t="str">
         <f aca="false">IF(F48&gt;0,(C48-F48)*100/C48," ")</f>
         <v> </v>
       </c>
-      <c r="H48" s="82"/>
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D49" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G49" s="81" t="str">
+        <f aca="false">IF(F49&gt;0,C49-F49," ")</f>
+        <v> </v>
+      </c>
+      <c r="H49" s="82" t="str">
         <f aca="false">IF(F49&gt;0,(C49-F49)*100/C49," ")</f>
         <v> </v>
       </c>
-      <c r="H49" s="82"/>
     </row>
     <row r="50" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D50" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G50" s="81" t="str">
+        <f aca="false">IF(F50&gt;0,C50-F50," ")</f>
+        <v> </v>
+      </c>
+      <c r="H50" s="82" t="str">
         <f aca="false">IF(F50&gt;0,(C50-F50)*100/C50," ")</f>
         <v> </v>
       </c>
-      <c r="H50" s="82"/>
     </row>
     <row r="51" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D51" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G51" s="81" t="str">
+        <f aca="false">IF(F51&gt;0,C51-F51," ")</f>
+        <v> </v>
+      </c>
+      <c r="H51" s="82" t="str">
         <f aca="false">IF(F51&gt;0,(C51-F51)*100/C51," ")</f>
         <v> </v>
       </c>
-      <c r="H51" s="82"/>
     </row>
     <row r="52" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D52" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G52" s="81" t="str">
+        <f aca="false">IF(F52&gt;0,C52-F52," ")</f>
+        <v> </v>
+      </c>
+      <c r="H52" s="82" t="str">
         <f aca="false">IF(F52&gt;0,(C52-F52)*100/C52," ")</f>
         <v> </v>
       </c>
-      <c r="H52" s="82"/>
     </row>
     <row r="53" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D53" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G53" s="81" t="str">
+        <f aca="false">IF(F53&gt;0,C53-F53," ")</f>
+        <v> </v>
+      </c>
+      <c r="H53" s="82" t="str">
         <f aca="false">IF(F53&gt;0,(C53-F53)*100/C53," ")</f>
         <v> </v>
       </c>
-      <c r="H53" s="82"/>
     </row>
     <row r="54" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D54" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G54" s="81" t="str">
+        <f aca="false">IF(F54&gt;0,C54-F54," ")</f>
+        <v> </v>
+      </c>
+      <c r="H54" s="82" t="str">
         <f aca="false">IF(F54&gt;0,(C54-F54)*100/C54," ")</f>
         <v> </v>
       </c>
-      <c r="H54" s="82"/>
     </row>
     <row r="55" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D55" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G55" s="81" t="str">
+        <f aca="false">IF(F55&gt;0,C55-F55," ")</f>
+        <v> </v>
+      </c>
+      <c r="H55" s="82" t="str">
         <f aca="false">IF(F55&gt;0,(C55-F55)*100/C55," ")</f>
         <v> </v>
       </c>
-      <c r="H55" s="82"/>
     </row>
     <row r="56" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D56" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G56" s="81" t="str">
+        <f aca="false">IF(F56&gt;0,C56-F56," ")</f>
+        <v> </v>
+      </c>
+      <c r="H56" s="82" t="str">
         <f aca="false">IF(F56&gt;0,(C56-F56)*100/C56," ")</f>
         <v> </v>
       </c>
-      <c r="H56" s="82"/>
     </row>
     <row r="57" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D57" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G57" s="81" t="str">
+        <f aca="false">IF(F57&gt;0,C57-F57," ")</f>
+        <v> </v>
+      </c>
+      <c r="H57" s="82" t="str">
         <f aca="false">IF(F57&gt;0,(C57-F57)*100/C57," ")</f>
         <v> </v>
       </c>
-      <c r="H57" s="82"/>
     </row>
     <row r="58" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D58" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G58" s="81" t="str">
+        <f aca="false">IF(F58&gt;0,C58-F58," ")</f>
+        <v> </v>
+      </c>
+      <c r="H58" s="82" t="str">
         <f aca="false">IF(F58&gt;0,(C58-F58)*100/C58," ")</f>
         <v> </v>
       </c>
-      <c r="H58" s="82"/>
     </row>
     <row r="59" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D59" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G59" s="81" t="str">
+        <f aca="false">IF(F59&gt;0,C59-F59," ")</f>
+        <v> </v>
+      </c>
+      <c r="H59" s="82" t="str">
         <f aca="false">IF(F59&gt;0,(C59-F59)*100/C59," ")</f>
         <v> </v>
       </c>
-      <c r="H59" s="82"/>
     </row>
     <row r="60" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D60" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G60" s="81" t="str">
+        <f aca="false">IF(F60&gt;0,C60-F60," ")</f>
+        <v> </v>
+      </c>
+      <c r="H60" s="82" t="str">
         <f aca="false">IF(F60&gt;0,(C60-F60)*100/C60," ")</f>
         <v> </v>
       </c>
-      <c r="H60" s="82"/>
     </row>
     <row r="61" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D61" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G61" s="81" t="str">
+        <f aca="false">IF(F61&gt;0,C61-F61," ")</f>
+        <v> </v>
+      </c>
+      <c r="H61" s="82" t="str">
         <f aca="false">IF(F61&gt;0,(C61-F61)*100/C61," ")</f>
         <v> </v>
       </c>
-      <c r="H61" s="82"/>
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D62" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G62" s="81" t="str">
+        <f aca="false">IF(F62&gt;0,C62-F62," ")</f>
+        <v> </v>
+      </c>
+      <c r="H62" s="82" t="str">
         <f aca="false">IF(F62&gt;0,(C62-F62)*100/C62," ")</f>
         <v> </v>
       </c>
-      <c r="H62" s="82"/>
     </row>
     <row r="63" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D63" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G63" s="81" t="str">
+        <f aca="false">IF(F63&gt;0,C63-F63," ")</f>
+        <v> </v>
+      </c>
+      <c r="H63" s="82" t="str">
         <f aca="false">IF(F63&gt;0,(C63-F63)*100/C63," ")</f>
         <v> </v>
       </c>
-      <c r="H63" s="82"/>
     </row>
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D64" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G64" s="81" t="str">
+        <f aca="false">IF(F64&gt;0,C64-F64," ")</f>
+        <v> </v>
+      </c>
+      <c r="H64" s="82" t="str">
         <f aca="false">IF(F64&gt;0,(C64-F64)*100/C64," ")</f>
         <v> </v>
       </c>
-      <c r="H64" s="82"/>
     </row>
     <row r="65" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D65" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G65" s="81" t="str">
+        <f aca="false">IF(F65&gt;0,C65-F65," ")</f>
+        <v> </v>
+      </c>
+      <c r="H65" s="82" t="str">
         <f aca="false">IF(F65&gt;0,(C65-F65)*100/C65," ")</f>
         <v> </v>
       </c>
-      <c r="H65" s="82"/>
     </row>
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D66" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G66" s="81" t="str">
+        <f aca="false">IF(F66&gt;0,C66-F66," ")</f>
+        <v> </v>
+      </c>
+      <c r="H66" s="82" t="str">
         <f aca="false">IF(F66&gt;0,(C66-F66)*100/C66," ")</f>
         <v> </v>
       </c>
-      <c r="H66" s="82"/>
     </row>
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D67" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G67" s="81" t="str">
+        <f aca="false">IF(F67&gt;0,C67-F67," ")</f>
+        <v> </v>
+      </c>
+      <c r="H67" s="82" t="str">
         <f aca="false">IF(F67&gt;0,(C67-F67)*100/C67," ")</f>
         <v> </v>
       </c>
-      <c r="H67" s="82"/>
     </row>
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D68" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G68" s="81" t="str">
+        <f aca="false">IF(F68&gt;0,C68-F68," ")</f>
+        <v> </v>
+      </c>
+      <c r="H68" s="82" t="str">
         <f aca="false">IF(F68&gt;0,(C68-F68)*100/C68," ")</f>
         <v> </v>
       </c>
-      <c r="H68" s="82"/>
     </row>
     <row r="69" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D69" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G69" s="81" t="str">
+        <f aca="false">IF(F69&gt;0,C69-F69," ")</f>
+        <v> </v>
+      </c>
+      <c r="H69" s="82" t="str">
         <f aca="false">IF(F69&gt;0,(C69-F69)*100/C69," ")</f>
         <v> </v>
       </c>
-      <c r="H69" s="82"/>
     </row>
     <row r="70" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D70" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G70" s="81" t="str">
+        <f aca="false">IF(F70&gt;0,C70-F70," ")</f>
+        <v> </v>
+      </c>
+      <c r="H70" s="82" t="str">
         <f aca="false">IF(F70&gt;0,(C70-F70)*100/C70," ")</f>
         <v> </v>
       </c>
-      <c r="H70" s="82"/>
     </row>
     <row r="71" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D71" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G71" s="81" t="str">
+        <f aca="false">IF(F71&gt;0,C71-F71," ")</f>
+        <v> </v>
+      </c>
+      <c r="H71" s="82" t="str">
         <f aca="false">IF(F71&gt;0,(C71-F71)*100/C71," ")</f>
         <v> </v>
       </c>
-      <c r="H71" s="82"/>
     </row>
     <row r="72" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D72" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G72" s="81" t="str">
+        <f aca="false">IF(F72&gt;0,C72-F72," ")</f>
+        <v> </v>
+      </c>
+      <c r="H72" s="82" t="str">
         <f aca="false">IF(F72&gt;0,(C72-F72)*100/C72," ")</f>
         <v> </v>
       </c>
-      <c r="H72" s="82"/>
     </row>
     <row r="73" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D73" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G73" s="81" t="str">
+        <f aca="false">IF(F73&gt;0,C73-F73," ")</f>
+        <v> </v>
+      </c>
+      <c r="H73" s="82" t="str">
         <f aca="false">IF(F73&gt;0,(C73-F73)*100/C73," ")</f>
         <v> </v>
       </c>
-      <c r="H73" s="82"/>
     </row>
     <row r="74" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D74" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G74" s="81" t="str">
+        <f aca="false">IF(F74&gt;0,C74-F74," ")</f>
+        <v> </v>
+      </c>
+      <c r="H74" s="82" t="str">
         <f aca="false">IF(F74&gt;0,(C74-F74)*100/C74," ")</f>
         <v> </v>
       </c>
-      <c r="H74" s="82"/>
     </row>
     <row r="75" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D75" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G75" s="81" t="str">
+        <f aca="false">IF(F75&gt;0,C75-F75," ")</f>
+        <v> </v>
+      </c>
+      <c r="H75" s="82" t="str">
         <f aca="false">IF(F75&gt;0,(C75-F75)*100/C75," ")</f>
         <v> </v>
       </c>
-      <c r="H75" s="82"/>
     </row>
     <row r="76" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D76" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G76" s="81" t="str">
+        <f aca="false">IF(F76&gt;0,C76-F76," ")</f>
+        <v> </v>
+      </c>
+      <c r="H76" s="82" t="str">
         <f aca="false">IF(F76&gt;0,(C76-F76)*100/C76," ")</f>
         <v> </v>
       </c>
-      <c r="H76" s="82"/>
     </row>
     <row r="77" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D77" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G77" s="81" t="str">
+        <f aca="false">IF(F77&gt;0,C77-F77," ")</f>
+        <v> </v>
+      </c>
+      <c r="H77" s="82" t="str">
         <f aca="false">IF(F77&gt;0,(C77-F77)*100/C77," ")</f>
         <v> </v>
       </c>
-      <c r="H77" s="82"/>
     </row>
     <row r="78" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D78" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G78" s="81" t="str">
+        <f aca="false">IF(F78&gt;0,C78-F78," ")</f>
+        <v> </v>
+      </c>
+      <c r="H78" s="82" t="str">
         <f aca="false">IF(F78&gt;0,(C78-F78)*100/C78," ")</f>
         <v> </v>
       </c>
-      <c r="H78" s="82"/>
     </row>
     <row r="79" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D79" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G79" s="81" t="str">
+        <f aca="false">IF(F79&gt;0,C79-F79," ")</f>
+        <v> </v>
+      </c>
+      <c r="H79" s="82" t="str">
         <f aca="false">IF(F79&gt;0,(C79-F79)*100/C79," ")</f>
         <v> </v>
       </c>
-      <c r="H79" s="82"/>
     </row>
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D80" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G80" s="81" t="str">
+        <f aca="false">IF(F80&gt;0,C80-F80," ")</f>
+        <v> </v>
+      </c>
+      <c r="H80" s="82" t="str">
         <f aca="false">IF(F80&gt;0,(C80-F80)*100/C80," ")</f>
         <v> </v>
       </c>
-      <c r="H80" s="82"/>
     </row>
     <row r="81" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D81" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G81" s="81" t="str">
+        <f aca="false">IF(F81&gt;0,C81-F81," ")</f>
+        <v> </v>
+      </c>
+      <c r="H81" s="82" t="str">
         <f aca="false">IF(F81&gt;0,(C81-F81)*100/C81," ")</f>
         <v> </v>
       </c>
-      <c r="H81" s="82"/>
     </row>
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D82" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G82" s="81" t="str">
+        <f aca="false">IF(F82&gt;0,C82-F82," ")</f>
+        <v> </v>
+      </c>
+      <c r="H82" s="82" t="str">
         <f aca="false">IF(F82&gt;0,(C82-F82)*100/C82," ")</f>
         <v> </v>
       </c>
-      <c r="H82" s="82"/>
     </row>
     <row r="83" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D83" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G83" s="81" t="str">
+        <f aca="false">IF(F83&gt;0,C83-F83," ")</f>
+        <v> </v>
+      </c>
+      <c r="H83" s="82" t="str">
         <f aca="false">IF(F83&gt;0,(C83-F83)*100/C83," ")</f>
         <v> </v>
       </c>
-      <c r="H83" s="82"/>
     </row>
     <row r="84" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D84" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G84" s="81" t="str">
+        <f aca="false">IF(F84&gt;0,C84-F84," ")</f>
+        <v> </v>
+      </c>
+      <c r="H84" s="82" t="str">
         <f aca="false">IF(F84&gt;0,(C84-F84)*100/C84," ")</f>
         <v> </v>
       </c>
-      <c r="H84" s="82"/>
     </row>
     <row r="85" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D85" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G85" s="81" t="str">
+        <f aca="false">IF(F85&gt;0,C85-F85," ")</f>
+        <v> </v>
+      </c>
+      <c r="H85" s="82" t="str">
         <f aca="false">IF(F85&gt;0,(C85-F85)*100/C85," ")</f>
         <v> </v>
       </c>
-      <c r="H85" s="82"/>
     </row>
     <row r="86" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D86" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G86" s="81" t="str">
+        <f aca="false">IF(F86&gt;0,C86-F86," ")</f>
+        <v> </v>
+      </c>
+      <c r="H86" s="82" t="str">
         <f aca="false">IF(F86&gt;0,(C86-F86)*100/C86," ")</f>
         <v> </v>
       </c>
-      <c r="H86" s="82"/>
     </row>
     <row r="87" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D87" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G87" s="81" t="str">
+        <f aca="false">IF(F87&gt;0,C87-F87," ")</f>
+        <v> </v>
+      </c>
+      <c r="H87" s="82" t="str">
         <f aca="false">IF(F87&gt;0,(C87-F87)*100/C87," ")</f>
         <v> </v>
       </c>
-      <c r="H87" s="82"/>
     </row>
     <row r="88" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D88" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G88" s="81" t="str">
+        <f aca="false">IF(F88&gt;0,C88-F88," ")</f>
+        <v> </v>
+      </c>
+      <c r="H88" s="82" t="str">
         <f aca="false">IF(F88&gt;0,(C88-F88)*100/C88," ")</f>
         <v> </v>
       </c>
-      <c r="H88" s="82"/>
     </row>
     <row r="89" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D89" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G89" s="81" t="str">
+        <f aca="false">IF(F89&gt;0,C89-F89," ")</f>
+        <v> </v>
+      </c>
+      <c r="H89" s="82" t="str">
         <f aca="false">IF(F89&gt;0,(C89-F89)*100/C89," ")</f>
         <v> </v>
       </c>
-      <c r="H89" s="82"/>
     </row>
     <row r="90" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D90" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G90" s="81" t="str">
+        <f aca="false">IF(F90&gt;0,C90-F90," ")</f>
+        <v> </v>
+      </c>
+      <c r="H90" s="82" t="str">
         <f aca="false">IF(F90&gt;0,(C90-F90)*100/C90," ")</f>
         <v> </v>
       </c>
-      <c r="H90" s="82"/>
     </row>
     <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D91" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G91" s="81" t="str">
+        <f aca="false">IF(F91&gt;0,C91-F91," ")</f>
+        <v> </v>
+      </c>
+      <c r="H91" s="82" t="str">
         <f aca="false">IF(F91&gt;0,(C91-F91)*100/C91," ")</f>
         <v> </v>
       </c>
-      <c r="H91" s="82"/>
     </row>
     <row r="92" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D92" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G92" s="81" t="str">
+        <f aca="false">IF(F92&gt;0,C92-F92," ")</f>
+        <v> </v>
+      </c>
+      <c r="H92" s="82" t="str">
         <f aca="false">IF(F92&gt;0,(C92-F92)*100/C92," ")</f>
         <v> </v>
       </c>
-      <c r="H92" s="82"/>
     </row>
     <row r="93" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D93" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G93" s="81" t="str">
+        <f aca="false">IF(F93&gt;0,C93-F93," ")</f>
+        <v> </v>
+      </c>
+      <c r="H93" s="82" t="str">
         <f aca="false">IF(F93&gt;0,(C93-F93)*100/C93," ")</f>
         <v> </v>
       </c>
-      <c r="H93" s="82"/>
     </row>
     <row r="94" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D94" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G94" s="81" t="str">
+        <f aca="false">IF(F94&gt;0,C94-F94," ")</f>
+        <v> </v>
+      </c>
+      <c r="H94" s="82" t="str">
         <f aca="false">IF(F94&gt;0,(C94-F94)*100/C94," ")</f>
         <v> </v>
       </c>
-      <c r="H94" s="82"/>
     </row>
     <row r="95" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D95" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G95" s="81" t="str">
+        <f aca="false">IF(F95&gt;0,C95-F95," ")</f>
+        <v> </v>
+      </c>
+      <c r="H95" s="82" t="str">
         <f aca="false">IF(F95&gt;0,(C95-F95)*100/C95," ")</f>
         <v> </v>
       </c>
-      <c r="H95" s="82"/>
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D96" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G96" s="81" t="str">
+        <f aca="false">IF(F96&gt;0,C96-F96," ")</f>
+        <v> </v>
+      </c>
+      <c r="H96" s="82" t="str">
         <f aca="false">IF(F96&gt;0,(C96-F96)*100/C96," ")</f>
         <v> </v>
       </c>
-      <c r="H96" s="82"/>
     </row>
     <row r="97" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D97" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G97" s="81" t="str">
+        <f aca="false">IF(F97&gt;0,C97-F97," ")</f>
+        <v> </v>
+      </c>
+      <c r="H97" s="82" t="str">
         <f aca="false">IF(F97&gt;0,(C97-F97)*100/C97," ")</f>
         <v> </v>
       </c>
-      <c r="H97" s="82"/>
     </row>
     <row r="98" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D98" s="78" t="n">
         <v>20</v>
       </c>
       <c r="G98" s="81" t="str">
+        <f aca="false">IF(F98&gt;0,C98-F98," ")</f>
+        <v> </v>
+      </c>
+      <c r="H98" s="82" t="str">
         <f aca="false">IF(F98&gt;0,(C98-F98)*100/C98," ")</f>
         <v> </v>
       </c>
-      <c r="H98" s="82"/>
     </row>
     <row r="99" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="83"/>
@@ -8684,10 +8963,13 @@
       </c>
       <c r="F99" s="85"/>
       <c r="G99" s="86" t="str">
+        <f aca="false">IF(F99&gt;0,C99-F99," ")</f>
+        <v> </v>
+      </c>
+      <c r="H99" s="87" t="str">
         <f aca="false">IF(F99&gt;0,(C99-F99)*100/C99," ")</f>
         <v> </v>
       </c>
-      <c r="H99" s="87"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/examples/ltd-latest/Salesinvoice.xlsx
+++ b/examples/ltd-latest/Salesinvoice.xlsx
@@ -642,7 +642,7 @@
     <t xml:space="preserve">VAT Registration Number</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
+    <t xml:space="preserve">123456789</t>
   </si>
   <si>
     <t xml:space="preserve">Not VAT registered? Enter single space in B11</t>
@@ -1685,7 +1685,7 @@
       <c r="N8" s="14"/>
       <c r="O8" s="15" t="str">
         <f aca="false">IF('Business Details'!B11&gt;0,'Business Details'!B11," ")</f>
-        <v>  </v>
+        <v>123456789</v>
       </c>
       <c r="P8" s="15"/>
       <c r="Q8" s="12"/>
@@ -1744,9 +1744,9 @@
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
-      <c r="C12" s="20" t="str">
+      <c r="C12" s="20" t="e">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N29,'Customer Details'!A:A,'Customer Details'!C:C)))</f>
-        <v> </v>
+        <v>#N/A</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
@@ -1790,9 +1790,9 @@
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
-      <c r="C14" s="20" t="str">
+      <c r="C14" s="20" t="e">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N29,'Customer Details'!A:A,'Customer Details'!D:D)))</f>
-        <v> </v>
+        <v>#N/A</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
@@ -1836,9 +1836,9 @@
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
-      <c r="C16" s="20" t="str">
+      <c r="C16" s="20" t="e">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N29,'Customer Details'!A:A,'Customer Details'!E:E)))</f>
-        <v> </v>
+        <v>#N/A</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
@@ -1882,9 +1882,9 @@
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
-      <c r="C18" s="20" t="str">
+      <c r="C18" s="20" t="e">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N29,'Customer Details'!A:A,'Customer Details'!F:F)))</f>
-        <v> </v>
+        <v>#N/A</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
@@ -1928,9 +1928,9 @@
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
-      <c r="C20" s="20" t="str">
+      <c r="C20" s="20" t="e">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N29,'Customer Details'!A:A,'Customer Details'!G:G)))</f>
-        <v> </v>
+        <v>#N/A</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="20"/>
@@ -2072,9 +2072,9 @@
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
-      <c r="C27" s="20" t="str">
+      <c r="C27" s="20" t="e">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N29,'Customer Details'!A:A,'Customer Details'!I:I)))</f>
-        <v> </v>
+        <v>#N/A</v>
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="20"/>
@@ -2086,9 +2086,9 @@
       <c r="K27" s="31"/>
       <c r="L27" s="31"/>
       <c r="M27" s="17"/>
-      <c r="N27" s="32" t="str">
+      <c r="N27" s="32" t="n">
         <f aca="false">IF(SUM('Invoice Database'!A:A)=0," ",LOOKUP(1,'Invoice Database'!A:A,'Invoice Database'!B:B))</f>
-        <v> </v>
+        <v>1</v>
       </c>
       <c r="O27" s="32"/>
       <c r="P27" s="32"/>
@@ -2116,9 +2116,9 @@
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
-      <c r="C29" s="20" t="str">
+      <c r="C29" s="20" t="e">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N29,'Customer Details'!A:A,'Customer Details'!J:J)))</f>
-        <v> </v>
+        <v>#N/A</v>
       </c>
       <c r="D29" s="20"/>
       <c r="E29" s="20"/>
@@ -2130,9 +2130,9 @@
       <c r="K29" s="31"/>
       <c r="L29" s="31"/>
       <c r="M29" s="17"/>
-      <c r="N29" s="32" t="str">
+      <c r="N29" s="32" t="n">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N27,'Invoice Database'!B:B,'Invoice Database'!D:D)))</f>
-        <v> </v>
+        <v>0</v>
       </c>
       <c r="O29" s="32"/>
       <c r="P29" s="32"/>
@@ -2160,9 +2160,9 @@
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
-      <c r="C31" s="20" t="str">
+      <c r="C31" s="20" t="e">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N29,'Customer Details'!A:A,'Customer Details'!K:K)))</f>
-        <v> </v>
+        <v>#N/A</v>
       </c>
       <c r="D31" s="20"/>
       <c r="E31" s="20"/>
@@ -2174,9 +2174,9 @@
       <c r="K31" s="31"/>
       <c r="L31" s="31"/>
       <c r="M31" s="17"/>
-      <c r="N31" s="32" t="str">
+      <c r="N31" s="32" t="e">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N29,'Customer Details'!A:A,'Customer Details'!B:B)))</f>
-        <v> </v>
+        <v>#N/A</v>
       </c>
       <c r="O31" s="32"/>
       <c r="P31" s="32"/>
@@ -2204,9 +2204,9 @@
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
-      <c r="C33" s="20" t="str">
+      <c r="C33" s="20" t="e">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N29,'Customer Details'!A:A,'Customer Details'!L:L)))</f>
-        <v> </v>
+        <v>#N/A</v>
       </c>
       <c r="D33" s="20"/>
       <c r="E33" s="20"/>
@@ -2218,9 +2218,9 @@
       <c r="K33" s="33"/>
       <c r="L33" s="33"/>
       <c r="M33" s="17"/>
-      <c r="N33" s="34" t="str">
+      <c r="N33" s="34" t="n">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N27,'Invoice Database'!B:B,'Invoice Database'!C:C)))</f>
-        <v> </v>
+        <v>0</v>
       </c>
       <c r="O33" s="34"/>
       <c r="P33" s="34"/>
@@ -2242,9 +2242,9 @@
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3"/>
-      <c r="C35" s="20" t="str">
+      <c r="C35" s="20" t="e">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,LOOKUP(N29,'Customer Details'!A:A,'Customer Details'!M:M)))</f>
-        <v> </v>
+        <v>#N/A</v>
       </c>
       <c r="D35" s="20"/>
       <c r="E35" s="20"/>
@@ -2294,44 +2294,44 @@
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="39" t="str">
+      <c r="C38" s="39" t="n">
         <f aca="false">IF(N27=" "," ",IF(LOOKUP(1,'Invoice Database'!A:A,'Invoice Database'!F:F)&gt;0,LOOKUP(1,'Invoice Database'!A:A,'Invoice Database'!F:F)," "))</f>
-        <v> </v>
+        <v>1001</v>
       </c>
       <c r="D38" s="40"/>
-      <c r="E38" s="41" t="str">
+      <c r="E38" s="41" t="n">
         <f aca="false">IF(C38=" "," ",LOOKUP(C38,'Product Details'!A:A,'Product Details'!B:B))</f>
-        <v> </v>
+        <v>0</v>
       </c>
       <c r="F38" s="41"/>
       <c r="G38" s="41"/>
       <c r="H38" s="41"/>
       <c r="I38" s="42"/>
-      <c r="J38" s="43" t="str">
+      <c r="J38" s="43" t="n">
         <f aca="false">IF(C38=" "," ",LOOKUP(C38,'Product Details'!A:A,'Product Details'!C:C))</f>
-        <v> </v>
+        <v>1200</v>
       </c>
       <c r="K38" s="44"/>
-      <c r="L38" s="45" t="str">
+      <c r="L38" s="45" t="n">
         <f aca="false">IF(C38=" "," ",LOOKUP(1,'Invoice Database'!A:A,'Invoice Database'!G:G))</f>
-        <v> </v>
+        <v>1</v>
       </c>
       <c r="M38" s="40"/>
-      <c r="N38" s="46" t="str">
+      <c r="N38" s="46" t="n">
         <f aca="false">IF(O8=" "," ",IF(C38=" "," ",LOOKUP(C38,'Product Details'!A:A,'Product Details'!D:D)))</f>
-        <v> </v>
+        <v>20</v>
       </c>
       <c r="O38" s="47"/>
-      <c r="P38" s="48" t="str">
+      <c r="P38" s="48" t="n">
         <f aca="false">IF(L38=" "," ",J38*L38)</f>
-        <v> </v>
+        <v>1200</v>
       </c>
       <c r="Q38" s="48"/>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="V38" s="2" t="n">
         <f aca="false">IF(N38=" ",0,P38*N38/100)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3171,7 +3171,7 @@
       <c r="O58" s="17"/>
       <c r="P58" s="51" t="n">
         <f aca="false">SUM(P38:P57)</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="Q58" s="51"/>
       <c r="S58" s="3"/>
@@ -3206,9 +3206,9 @@
       <c r="M60" s="50"/>
       <c r="N60" s="50"/>
       <c r="O60" s="17"/>
-      <c r="P60" s="51" t="str">
+      <c r="P60" s="51" t="n">
         <f aca="false">IF(N27=" "," ",IF(N27&gt;0,IF(LOOKUP(N27,'Invoice Database'!B:B,'Invoice Database'!E:E)&gt;0,LOOKUP(N27,'Invoice Database'!B:B,'Invoice Database'!E:E),0)))</f>
-        <v> </v>
+        <v>37.5</v>
       </c>
       <c r="Q60" s="51"/>
       <c r="S60" s="3"/>
@@ -3244,8 +3244,8 @@
       <c r="N62" s="50"/>
       <c r="O62" s="17"/>
       <c r="P62" s="51" t="n">
-        <f aca="false">IF(P58&lt;&gt;0,SUM(V38:V57)+P60*0.2,0)</f>
-        <v>0</v>
+        <f aca="false">IF(P58&lt;&gt;0,SUM(V38:V57)+P60*'Product Details'!$D$2/100,0)</f>
+        <v>247.5</v>
       </c>
       <c r="Q62" s="51"/>
       <c r="S62" s="3"/>
@@ -3283,7 +3283,7 @@
       <c r="O64" s="55"/>
       <c r="P64" s="56" t="n">
         <f aca="false">SUM(P58:Q62)</f>
-        <v>0</v>
+        <v>1485</v>
       </c>
       <c r="Q64" s="56"/>
       <c r="S64" s="3"/>
@@ -3514,7 +3514,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AS1"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="62" width="9.82"/>
@@ -3661,6 +3661,23 @@
       </c>
       <c r="AS1" s="68" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="65" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F2" s="63" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G2" s="63" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7694,6 +7711,9 @@
       <c r="A2" s="63" t="n">
         <v>1001</v>
       </c>
+      <c r="C2" s="77" t="n">
+        <v>1200</v>
+      </c>
       <c r="D2" s="78" t="n">
         <v>20</v>
       </c>

--- a/examples/ltd-latest/Salesinvoice.xlsx
+++ b/examples/ltd-latest/Salesinvoice.xlsx
@@ -409,7 +409,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="90">
   <si>
     <t xml:space="preserve">SALES INVOICE</t>
   </si>
@@ -631,6 +631,9 @@
   </si>
   <si>
     <t xml:space="preserve">Telephone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0161 555 0100</t>
   </si>
   <si>
     <t xml:space="preserve">Fax number</t>
@@ -1947,7 +1950,7 @@
       <c r="M20" s="11"/>
       <c r="N20" s="24" t="str">
         <f aca="false">IF('Business Details'!B8&gt;0,'Business Details'!B8," ")</f>
-        <v> </v>
+        <v>0161 555 0100</v>
       </c>
       <c r="O20" s="24"/>
       <c r="P20" s="24"/>
@@ -9088,72 +9091,74 @@
       <c r="A8" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="93"/>
+      <c r="B8" s="93" t="s">
+        <v>74</v>
+      </c>
       <c r="C8" s="89"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="90" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="93"/>
       <c r="C9" s="89"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="90" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B10" s="94"/>
       <c r="C10" s="89"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="90" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="95" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" s="89"/>
       <c r="D11" s="92" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="90" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="91"/>
       <c r="C12" s="89"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="90" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B13" s="91" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" s="89"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="90" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B14" s="91" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" s="89"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="90" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" s="91" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" s="89"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="90" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B16" s="91"/>
       <c r="C16" s="89"/>
@@ -9165,7 +9170,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="90" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B17" s="96" t="str">
         <f aca="false">"All goods remain the property of "&amp;B3&amp;" until paid for in full"</f>
@@ -9180,7 +9185,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="90" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B18" s="96"/>
       <c r="C18" s="96"/>

--- a/examples/ltd-latest/Salesinvoice.xlsx
+++ b/examples/ltd-latest/Salesinvoice.xlsx
@@ -409,7 +409,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="89">
   <si>
     <t xml:space="preserve">SALES INVOICE</t>
   </si>
@@ -631,9 +631,6 @@
   </si>
   <si>
     <t xml:space="preserve">Telephone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0161 555 0100</t>
   </si>
   <si>
     <t xml:space="preserve">Fax number</t>
@@ -1950,7 +1947,7 @@
       <c r="M20" s="11"/>
       <c r="N20" s="24" t="str">
         <f aca="false">IF('Business Details'!B8&gt;0,'Business Details'!B8," ")</f>
-        <v>0161 555 0100</v>
+        <v> </v>
       </c>
       <c r="O20" s="24"/>
       <c r="P20" s="24"/>
@@ -9091,74 +9088,72 @@
       <c r="A8" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="93" t="s">
-        <v>74</v>
-      </c>
+      <c r="B8" s="93"/>
       <c r="C8" s="89"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="90" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="93"/>
       <c r="C9" s="89"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="90" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="94"/>
       <c r="C10" s="89"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="90" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="95" t="s">
         <v>77</v>
-      </c>
-      <c r="B11" s="95" t="s">
-        <v>78</v>
       </c>
       <c r="C11" s="89"/>
       <c r="D11" s="92" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12" s="91"/>
       <c r="C12" s="89"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="90" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="91" t="s">
         <v>81</v>
-      </c>
-      <c r="B13" s="91" t="s">
-        <v>82</v>
       </c>
       <c r="C13" s="89"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="91" t="s">
         <v>83</v>
-      </c>
-      <c r="B14" s="91" t="s">
-        <v>84</v>
       </c>
       <c r="C14" s="89"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="91" t="s">
         <v>85</v>
-      </c>
-      <c r="B15" s="91" t="s">
-        <v>86</v>
       </c>
       <c r="C15" s="89"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="90" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" s="91"/>
       <c r="C16" s="89"/>
@@ -9170,7 +9165,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B17" s="96" t="str">
         <f aca="false">"All goods remain the property of "&amp;B3&amp;" until paid for in full"</f>
@@ -9185,7 +9180,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="90" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B18" s="96"/>
       <c r="C18" s="96"/>
